--- a/samples/ss_pedan12_ingest.xlsx
+++ b/samples/ss_pedan12_ingest.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/samples/ss_pedan12_ingest.xlsx
+++ b/samples/ss_pedan12_ingest.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U18"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IBT 1,2 Pedan 500/150 kV</t>
+          <t>IBT 1 Pedan 500/150 kV</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,14 +700,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2 IBT (unit 1,2)</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
@@ -738,31 +734,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pedan (bus 150 kV)</t>
+          <t>IBT 2 Pedan 500/150 kV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>IBT 2 PEDAN7</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>PEDAN7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>PEDAN</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -779,7 +789,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -795,12 +805,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Klaten</t>
+          <t>Pedan (bus 150 kV)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KLATN</t>
+          <t>PEDAN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -809,7 +819,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -836,7 +846,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -852,12 +862,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kalasan</t>
+          <t>Klaten</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KLASN</t>
+          <t>KLATN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -866,7 +876,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -893,7 +903,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -909,12 +919,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bantul</t>
+          <t>Kalasan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BANTL</t>
+          <t>KLASN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -923,7 +933,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -950,7 +960,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>6;8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -966,12 +976,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Semanu</t>
+          <t>Bantul</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SMANU</t>
+          <t>BANTL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -980,7 +990,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1002,10 +1012,14 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>6;8</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1019,12 +1033,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jajar</t>
+          <t>Semanu</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>JAJAR</t>
+          <t>SMANU</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1033,7 +1047,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1055,14 +1069,10 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1076,12 +1086,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mangkunegaran (rencana)</t>
+          <t>Jajar</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MKRAN</t>
+          <t>JAJAR</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1090,7 +1100,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1106,16 +1116,20 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Rencana</t>
+          <t>Beroperasi</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1129,12 +1143,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Gondangrejo</t>
+          <t>Mangkunegaran</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GDRJO</t>
+          <t>MKRAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1165,14 +1179,10 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1186,12 +1196,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Palur</t>
+          <t>Gondangrejo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PALUR</t>
+          <t>GDRJO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1200,7 +1210,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1227,7 +1237,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>4;7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1243,12 +1253,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ampel (SS Boyolali)</t>
+          <t>Palur</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AMPEL</t>
+          <t>PALUR</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1257,7 +1267,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1269,28 +1279,24 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>batas ke Subsistem Boyolali 1,2</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>4;7</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1304,12 +1310,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bendono (SS Boyolali)</t>
+          <t>Ampel (SS Boyolali)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BDONO</t>
+          <t>AMPEL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1365,12 +1371,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wates (SS Kesugihan)</t>
+          <t>Bendono (SS Boyolali)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>WATES</t>
+          <t>BDONO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1379,7 +1385,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1393,7 +1399,7 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>batas ke Subsistem Kesugihan 1,2</t>
+          <t>batas ke Subsistem Boyolali 1,2</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1426,12 +1432,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wonosari/Gedean (SS Pedan 3,4)</t>
+          <t>Wates (SS Kesugihan)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>WBJAN</t>
+          <t>WATES</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1454,7 +1460,7 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>batas ke Subsistem Pedan 3,4</t>
+          <t>batas ke Subsistem Kesugihan 1,2</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -1487,12 +1493,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Solo Baru (SS Pedan 3,4)</t>
+          <t>Wonosari/Gedean (SS Pedan 3,4)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SLBRU</t>
+          <t>WBJAN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1548,12 +1554,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Masaran (SS Pedan 3,4)</t>
+          <t>Solo Baru (SS Pedan 3,4)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MSRAN</t>
+          <t>SLBRU</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1602,6 +1608,67 @@
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Masaran (SS Pedan 3,4)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MSRAN</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>batas ke Subsistem Pedan 3,4</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2262,7 +2329,7 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SUTT Jajar - Mangkunegaran (belum energize)</t>
+          <t>SKTT Jajar - Mangkunegaran</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2286,12 +2353,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Rencana</t>
+          <t>Beroperasi</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Rawan</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -2659,12 +2726,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[N-1] Pola Operasi Bus Section SS Pedan 1,2 &amp; SS Pedan 3,4 belum sesuai</t>
+          <t>[BELUM_DITETAPKAN] Pola Operasi Bus Section SS Pedan 1,2 &amp; SS Pedan 3,4 belum sesuai</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2834,12 +2901,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[N-1] 1.Pembebanan Trafo di GI 150 kV Palur &gt;80% dan tidak dapat dilakukan extension penambahan bay trafo baru karena keterbatasan lahan di GI tersebut. 2.Keterbatasan feeder 20 kV di GI 150 kV Masaran dan GI 150 kV Palur</t>
+          <t>[BELUM_DITETAPKAN] 1.Pembebanan Trafo di GI 150 kV Palur &gt;80% dan tidak dapat dilakukan extension penambahan bay trafo baru karena keterbatasan lahan di GI tersebut. 2.Keterbatasan feeder 20 kV di GI 150 kV Masaran dan GI 150 kV Palur</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
